--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-observation-survey-document.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-observation-survey-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6066" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6066" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2162,10 +2162,6 @@
   </si>
   <si>
     <t>Notes for this resource/element</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Observation.component:ComposantN1.modifierExtension</t>
@@ -19315,7 +19311,7 @@
         <v>81</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>144</v>
@@ -19367,7 +19363,7 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="L141" t="s" s="2">
         <v>222</v>
@@ -19433,7 +19429,7 @@
         <v>93</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>82</v>
@@ -19789,7 +19785,7 @@
         <v>93</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>688</v>
+        <v>82</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>105</v>
@@ -19815,7 +19811,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>646</v>
@@ -19937,7 +19933,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>647</v>
@@ -19966,7 +19962,7 @@
         <v>211</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M146" t="s" s="2">
         <v>649</v>
@@ -20059,7 +20055,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>654</v>
@@ -20088,7 +20084,7 @@
         <v>493</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="M147" t="s" s="2">
         <v>495</v>
@@ -20181,7 +20177,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>658</v>
@@ -20303,7 +20299,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>662</v>
@@ -20425,7 +20421,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>664</v>
@@ -20547,13 +20543,13 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>636</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>82</v>
@@ -20578,7 +20574,7 @@
         <v>571</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="M151" t="s" s="2">
         <v>638</v>
@@ -20671,7 +20667,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>644</v>
@@ -20789,7 +20785,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>645</v>
@@ -20909,7 +20905,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>646</v>
@@ -21031,7 +21027,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>647</v>
@@ -21060,7 +21056,7 @@
         <v>211</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M155" t="s" s="2">
         <v>649</v>
@@ -21153,7 +21149,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>654</v>
@@ -21182,7 +21178,7 @@
         <v>493</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="M156" t="s" s="2">
         <v>495</v>
@@ -21275,7 +21271,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>658</v>
@@ -21397,7 +21393,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>662</v>
@@ -21519,7 +21515,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>664</v>
